--- a/data/trans_orig/IP19C04-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP19C04-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>721</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6350</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>676</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5999</t>
+          <t>5897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8805</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13201</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>18600</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,33%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>20621</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25839</t>
+          <t>25842</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,38%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>37034</t>
+          <t>36698</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43779</t>
+          <t>43661</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,25%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>638</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>5700</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1971</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>3780</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12151</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51031</t>
+          <t>51522</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>56566</t>
+          <t>56584</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>55777</t>
+          <t>56311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>63004</t>
+          <t>62999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>110046</t>
+          <t>110381</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>118425</t>
+          <t>118417</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>749</t>
+          <t>785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6702</t>
+          <t>7553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>1379</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7846</t>
+          <t>8083</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27590</t>
+          <t>26739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33543</t>
+          <t>33507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>32040</t>
+          <t>31764</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>61775</t>
+          <t>61538</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>68415</t>
+          <t>68242</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1182</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7040</t>
+          <t>6850</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34919</t>
+          <t>35109</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40887</t>
+          <t>40777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>36829</t>
+          <t>36937</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>74099</t>
+          <t>74677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>81589</t>
+          <t>81720</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>733</t>
+          <t>730</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>6987</t>
+          <t>6653</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>729</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7009</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15480</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21734</t>
+          <t>21737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41650</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>47935</t>
+          <t>47930</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,5%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>634</t>
+          <t>625</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5230</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>18,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>666</t>
+          <t>660</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5930</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,05%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>8627</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>20623</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24706</t>
+          <t>24715</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>22390</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27692</t>
+          <t>27698</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>79,09%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>44708</t>
+          <t>45071</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>51724</t>
+          <t>51716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,31%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>732</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7061</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9747</t>
+          <t>9066</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>12917</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>58178</t>
+          <t>58223</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>64542</t>
+          <t>64552</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58282</t>
+          <t>58963</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65949</t>
+          <t>65941</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>119761</t>
+          <t>120397</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>129027</t>
+          <t>129123</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1583</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>9198</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3172</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11310</t>
+          <t>11235</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16354</t>
+          <t>16276</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,45%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71997</t>
+          <t>72122</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>79737</t>
+          <t>79415</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63103</t>
+          <t>63178</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>71081</t>
+          <t>71241</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>139380</t>
+          <t>139458</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>149545</t>
+          <t>149443</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>14119</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>28552</t>
+          <t>28870</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>18465</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>34049</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>36529</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58819</t>
+          <t>56580</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>322378</t>
+          <t>322060</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>336811</t>
+          <t>337075</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>326658</t>
+          <t>327682</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>342638</t>
+          <t>343266</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>653842</t>
+          <t>656081</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>676132</t>
+          <t>677061</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,0%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>545</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>1352</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7920</t>
+          <t>8283</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10675</t>
+          <t>10386</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17271</t>
+          <t>17129</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>21834</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>76,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21739</t>
+          <t>21376</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>28166</t>
+          <t>28307</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41359</t>
+          <t>41648</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49147</t>
+          <t>48883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1326</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7528</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4622</t>
+          <t>4616</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1938</t>
+          <t>1964</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8814</t>
+          <t>8728</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45516</t>
+          <t>45077</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>51705</t>
+          <t>51718</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53010</t>
+          <t>53016</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>101863</t>
+          <t>101949</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108739</t>
+          <t>108713</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,23%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>680</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>6911</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1348</t>
+          <t>1406</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26347</t>
+          <t>26552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32781</t>
+          <t>32783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35928</t>
+          <t>35703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4905,7 +4905,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>64779</t>
+          <t>64464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>71560</t>
+          <t>71502</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1058</t>
+          <t>1077</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>7098</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>465</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6215</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2321</t>
+          <t>2418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11031</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>12,79%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>35192</t>
+          <t>34700</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40740</t>
+          <t>40721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>34383</t>
+          <t>35011</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>40758</t>
+          <t>40761</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,7 +5248,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>71993</t>
+          <t>72402</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80703</t>
+          <t>80606</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3792</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5883</t>
+          <t>5270</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>705</t>
+          <t>801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7171</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,35%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22276</t>
+          <t>23227</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21747</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>46697</t>
+          <t>46527</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52993</t>
+          <t>52897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>699</t>
+          <t>706</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5895</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1439</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9042</t>
+          <t>9154</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3552</t>
+          <t>3455</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>29680</t>
+          <t>29531</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34727</t>
+          <t>34720</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24117</t>
+          <t>24005</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31350</t>
+          <t>31720</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>72,73%</t>
+          <t>72,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>56324</t>
+          <t>55968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65033</t>
+          <t>65130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>943</t>
+          <t>726</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7773</t>
+          <t>7639</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>630</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6285</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2332</t>
+          <t>2402</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>11504</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,77%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56196</t>
+          <t>56330</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63026</t>
+          <t>63243</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>60879</t>
+          <t>60184</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66539</t>
+          <t>66534</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>119374</t>
+          <t>119629</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>128801</t>
+          <t>128731</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>1837</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>8870</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6819</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13233</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>69387</t>
+          <t>68977</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>76013</t>
+          <t>76010</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,13%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>63268</t>
+          <t>63094</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>68810</t>
+          <t>68828</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>134701</t>
+          <t>134804</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>143551</t>
+          <t>143617</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>15861</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>31640</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>14294</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>29179</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>33571</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>55034</t>
+          <t>54266</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>322577</t>
+          <t>322351</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>338130</t>
+          <t>338332</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>336823</t>
+          <t>336429</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>350860</t>
+          <t>351708</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>664959</t>
+          <t>665727</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>686534</t>
+          <t>686422</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,46%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>602</t>
+          <t>588</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>6474</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6247</t>
+          <t>6788</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1794</t>
+          <t>1849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>14,93%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22828</t>
+          <t>22675</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>28561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24299</t>
+          <t>23758</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29901</t>
+          <t>29900</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,55%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50558</t>
+          <t>50782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>57901</t>
+          <t>57846</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8062</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9881</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>49748</t>
+          <t>49581</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48671</t>
+          <t>47649</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>55211</t>
+          <t>54709</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>100360</t>
+          <t>99887</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>108061</t>
+          <t>107599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3424</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28733</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>60912</t>
+          <t>61217</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2224</t>
+          <t>2163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>729</t>
+          <t>902</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7824</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>4453</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>13926</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,28%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36860</t>
+          <t>36687</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44321</t>
+          <t>44382</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43179</t>
+          <t>43739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>50274</t>
+          <t>50101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>83751</t>
+          <t>83622</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>93565</t>
+          <t>93095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -8791,7 +8791,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8806,7 +8806,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2831</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -8899,7 +8899,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>13962</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>29280</t>
+          <t>29568</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>717</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6254</t>
+          <t>6243</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5201</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1924</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8582</t>
+          <t>8660</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,78%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>33500</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39042</t>
+          <t>39026</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>35376</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -9257,7 +9257,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,18%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>71731</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78868</t>
+          <t>78389</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1338</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8076</t>
+          <t>8292</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1399</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>8623</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,66%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>59367</t>
+          <t>59151</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>66105</t>
+          <t>66009</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>120929</t>
+          <t>120763</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>127987</t>
+          <t>128067</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>8226</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>588</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5576</t>
+          <t>5498</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2722</t>
+          <t>2736</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11118</t>
+          <t>10310</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>71026</t>
+          <t>71479</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>77698</t>
+          <t>77859</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>73082</t>
+          <t>73160</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>78071</t>
+          <t>78070</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>146792</t>
+          <t>147600</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>155188</t>
+          <t>155174</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>13357</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>26731</t>
+          <t>27656</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>21615</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25371</t>
+          <t>25839</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>44038</t>
+          <t>43764</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>336470</t>
+          <t>335545</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>350131</t>
+          <t>349844</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>346901</t>
+          <t>347029</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>359626</t>
+          <t>359390</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>687807</t>
+          <t>688081</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>706474</t>
+          <t>706006</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>96,53%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>620</t>
+          <t>671</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10524</t>
+          <t>10141</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>664</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6529</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2122</t>
+          <t>2120</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>12458</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24294</t>
+          <t>24677</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34198</t>
+          <t>34147</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>33336</t>
+          <t>33985</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>39233</t>
+          <t>39201</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62224</t>
+          <t>62702</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72560</t>
+          <t>72562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,7 +10900,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5817</t>
+          <t>6873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>750</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8555</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>63027</t>
+          <t>61971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>68181</t>
+          <t>68844</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,7 +11193,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>69470</t>
+          <t>68269</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134118</t>
+          <t>134818</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>141923</t>
+          <t>141936</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>695</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6009</t>
+          <t>6085</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2378</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26361</t>
+          <t>26135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>31196</t>
+          <t>31192</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34043</t>
+          <t>33967</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>39336</t>
+          <t>39357</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>62269</t>
+          <t>62257</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>69496</t>
+          <t>69528</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,64%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,74%</t>
         </is>
       </c>
     </row>
@@ -11736,7 +11736,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11751,7 +11751,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6363</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11806,7 +11806,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -11844,7 +11844,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38350</t>
+          <t>38556</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>53142</t>
+          <t>52298</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>94270</t>
+          <t>94459</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -11929,7 +11929,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>449</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4028</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>447</t>
+          <t>440</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>4522</t>
+          <t>4190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21272</t>
+          <t>21264</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>24843</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>55397</t>
+          <t>55729</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>59472</t>
+          <t>59479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,45%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3503</t>
+          <t>3015</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>379</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4730</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>651</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6141</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23459</t>
+          <t>23947</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22214</t>
+          <t>21874</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>26585</t>
+          <t>26565</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,44%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>47766</t>
+          <t>48205</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53172</t>
+          <t>53256</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2416</t>
+          <t>2592</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>9899</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2450</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11705</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>6429</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18240</t>
+          <t>18478</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>68008</t>
+          <t>67857</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>75340</t>
+          <t>75164</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>96983</t>
+          <t>97461</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>106313</t>
+          <t>106238</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>168204</t>
+          <t>167966</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>180015</t>
+          <t>179906</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>90,22%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,49%</t>
         </is>
       </c>
     </row>
@@ -13108,7 +13108,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>5998</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5203</t>
+          <t>5160</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>828</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>7530</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>77391</t>
+          <t>77297</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -13231,7 +13231,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13251,7 +13251,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>96574</t>
+          <t>96617</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -13266,7 +13266,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>177542</t>
+          <t>177405</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>184240</t>
+          <t>184244</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11319</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27500</t>
+          <t>27037</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>9892</t>
+          <t>9669</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23604</t>
+          <t>23862</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>24239</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45601</t>
+          <t>45443</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>364133</t>
+          <t>364596</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>380314</t>
+          <t>379335</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>460840</t>
+          <t>460582</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>474552</t>
+          <t>474775</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>830475</t>
+          <t>830633</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>850884</t>
+          <t>851837</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,23%</t>
         </is>
       </c>
     </row>
